--- a/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week05_28Sep.xlsx
+++ b/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week05_28Sep.xlsx
@@ -1079,7 +1079,7 @@
     <row r="8" ht="45.75" customHeight="1" s="43">
       <c r="A8" s="51" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: Black History Month launches (Thu 1 Oct, runs to W8) — Build Humanities' BHM profile wall carries it; English picks up a BHM poem next week.  National Poetry Day Thu 1 Oct (tbc).  EVIDENCE: 'People Who Shaped Britain' wall + EFL: cultural → SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: Black History Month launches (Thu 1 Oct, runs to W8) — Build Humanities' BHM profile wall carries it; English picks up a BHM poem next week.  National Poetry Day Thu 1 Oct (tbc).  EVIDENCE: 'People Who Shaped Britain' wall + evidence platform: cultural → SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="52" t="n"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="I12" s="62" t="inlineStr">
         <is>
-          <t>TA pre-punches card and helps with split pins. Teacher says 'PULL' with a gesture every single time — GESTURE ANCHOR: fist pulled to shoulder = contract. LOOP [Feedback Policy]: Voice = build/feel/say 'pull' [VF, ?] → Audience: say what the muscle did; [R] once received → EVIDENCE: arm-model video clip, upload same day [E: science — daily EFL; banks ELC 8939].</t>
+          <t>TA pre-punches card and helps with split pins. Teacher says 'PULL' with a gesture every single time — GESTURE ANCHOR: fist pulled to shoulder = contract. LOOP [Feedback Policy]: Voice = build/feel/say 'pull' [VF, ?] → Audience: say what the muscle did; [R] once received → EVIDENCE: arm-model video clip, upload same day [E: science — daily evidence platform; banks ELC 8939].</t>
         </is>
       </c>
       <c r="J12" s="57" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I13" s="59" t="inlineStr">
         <is>
-          <t>TA plays the second character in freeze-frames and scribes choices.  LOOP [Feedback Policy]: Voice = freeze/choose/say why [VF] → Audience: name the risk spotted back; [R] when the pause is used for real → EVIDENCE: photos + card, same day [E: BV individual liberty — daily EFL; banks AQA UAS].</t>
+          <t>TA plays the second character in freeze-frames and scribes choices.  LOOP [Feedback Policy]: Voice = freeze/choose/say why [VF] → Audience: name the risk spotted back; [R] when the pause is used for real → EVIDENCE: photos + card, same day [E: BV individual liberty — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J13" s="59" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="I14" s="62" t="inlineStr">
         <is>
-          <t>TA runs the Christingle line and captures each explanation.  LOOP [Feedback Policy]: Voice = sort/race/earn-a-part [VF, ?] → Audience: name the symbol meaning back; [R] once received → EVIDENCE: photo + clip, same day [E: cultural — daily EFL].</t>
+          <t>TA runs the Christingle line and captures each explanation.  LOOP [Feedback Policy]: Voice = sort/race/earn-a-part [VF, ?] → Audience: name the symbol meaning back; [R] once received → EVIDENCE: photo + clip, same day [E: cultural — daily evidence platform].</t>
         </is>
       </c>
       <c r="J14" s="57" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I15" s="62" t="inlineStr">
         <is>
-          <t>TA challenges gently ('why higher than…?') and scribes each defence.  LOOP [Feedback Policy]: Voice = place/say the reason [VF, ?] → Audience: name the change-claim back; [R] once received → EVIDENCE: line photo + strips, same day [E: humanities — daily EFL; banks AQA UAS].</t>
+          <t>TA challenges gently ('why higher than…?') and scribes each defence.  LOOP [Feedback Policy]: Voice = place/say the reason [VF, ?] → Audience: name the change-claim back; [R] once received → EVIDENCE: line photo + strips, same day [E: humanities — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J15" s="57" t="inlineStr">
